--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LEYMA CORUÑA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LEYMA CORUÑA.xlsx
@@ -565,13 +565,13 @@
         <v>28</v>
       </c>
       <c r="D2" t="n">
-        <v>62.3529</v>
+        <v>61.5222</v>
       </c>
       <c r="E2" t="n">
-        <v>45.4536</v>
+        <v>44.5809</v>
       </c>
       <c r="F2" t="n">
-        <v>16.8996</v>
+        <v>16.9408</v>
       </c>
       <c r="G2" t="n">
         <v>28.1003</v>
@@ -610,13 +610,13 @@
         <v>32.4081</v>
       </c>
       <c r="S2" t="n">
-        <v>14.1803</v>
+        <v>13.3494</v>
       </c>
       <c r="T2" t="n">
-        <v>8.4001</v>
+        <v>7.527600000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>5.780200000000001</v>
+        <v>5.8217</v>
       </c>
       <c r="V2" t="n">
         <v>5.4997</v>
@@ -643,13 +643,13 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>53.108</v>
+        <v>53.1085</v>
       </c>
       <c r="E3" t="n">
-        <v>37.5894</v>
+        <v>37.2865</v>
       </c>
       <c r="F3" t="n">
-        <v>15.5186</v>
+        <v>15.8219</v>
       </c>
       <c r="G3" t="n">
         <v>37.9732</v>
@@ -688,13 +688,13 @@
         <v>28.928</v>
       </c>
       <c r="S3" t="n">
-        <v>8.458299999999999</v>
+        <v>8.4588</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1602</v>
+        <v>4.8574</v>
       </c>
       <c r="U3" t="n">
-        <v>3.2979</v>
+        <v>3.6016</v>
       </c>
       <c r="V3" t="n">
         <v>9.7219</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. JOU COLL</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>52.1276</v>
+        <v>52.1869</v>
       </c>
       <c r="E4" t="n">
-        <v>43.9683</v>
+        <v>48.3108</v>
       </c>
       <c r="F4" t="n">
-        <v>8.159299999999998</v>
+        <v>3.8767</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3961</v>
+        <v>44.3466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1717</v>
+        <v>13.6019</v>
       </c>
       <c r="I4" t="n">
-        <v>13.2243</v>
+        <v>30.7444</v>
       </c>
       <c r="J4" t="n">
-        <v>36.2591</v>
+        <v>74.6345</v>
       </c>
       <c r="K4" t="n">
-        <v>13.4393</v>
+        <v>28.835</v>
       </c>
       <c r="L4" t="n">
-        <v>22.8197</v>
+        <v>45.7995</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.8632</v>
+        <v>-30.2881</v>
       </c>
       <c r="N4" t="n">
-        <v>-13.2679</v>
+        <v>-15.2331</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.595700000000001</v>
+        <v>-15.055</v>
       </c>
       <c r="P4" t="n">
-        <v>30.8859</v>
+        <v>-11.5282</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12.8326</v>
+        <v>-58.7266</v>
       </c>
       <c r="R4" t="n">
-        <v>43.7186</v>
+        <v>47.1988</v>
       </c>
       <c r="S4" t="n">
-        <v>17.9809</v>
+        <v>5.8749</v>
       </c>
       <c r="T4" t="n">
-        <v>8.204000000000001</v>
+        <v>1.5746</v>
       </c>
       <c r="U4" t="n">
-        <v>9.776899999999999</v>
+        <v>4.3004</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.1351</v>
+        <v>13.494</v>
       </c>
       <c r="W4" t="n">
-        <v>12.3378</v>
+        <v>30.8287</v>
       </c>
       <c r="X4" t="n">
-        <v>-22.4728</v>
+        <v>-17.3345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>G. JOU COLL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>45.2788</v>
+        <v>51.0966</v>
       </c>
       <c r="E5" t="n">
-        <v>24.4566</v>
+        <v>42.8184</v>
       </c>
       <c r="F5" t="n">
-        <v>20.8222</v>
+        <v>8.278199999999998</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5366</v>
+        <v>13.3961</v>
       </c>
       <c r="H5" t="n">
-        <v>10.3362</v>
+        <v>0.1717</v>
       </c>
       <c r="I5" t="n">
-        <v>-12.8727</v>
+        <v>13.2243</v>
       </c>
       <c r="J5" t="n">
-        <v>12.5</v>
+        <v>36.2591</v>
       </c>
       <c r="K5" t="n">
-        <v>16.989</v>
+        <v>13.4393</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.489599999999999</v>
+        <v>22.8197</v>
       </c>
       <c r="M5" t="n">
-        <v>-15.0362</v>
+        <v>-22.8632</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.6528</v>
+        <v>-13.2679</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.383599999999999</v>
+        <v>-9.595700000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1753</v>
+        <v>30.8859</v>
       </c>
       <c r="Q5" t="n">
-        <v>-48.7213</v>
+        <v>-12.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>46.546</v>
+        <v>43.7186</v>
       </c>
       <c r="S5" t="n">
-        <v>40.4993</v>
+        <v>16.9499</v>
       </c>
       <c r="T5" t="n">
-        <v>24.765</v>
+        <v>7.0545</v>
       </c>
       <c r="U5" t="n">
-        <v>15.7344</v>
+        <v>9.8955</v>
       </c>
       <c r="V5" t="n">
-        <v>9.491299999999999</v>
+        <v>-10.1351</v>
       </c>
       <c r="W5" t="n">
-        <v>35.9135</v>
+        <v>12.3378</v>
       </c>
       <c r="X5" t="n">
-        <v>-26.4219</v>
+        <v>-22.4728</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. BARRO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>36.408</v>
+        <v>40.5914</v>
       </c>
       <c r="E6" t="n">
-        <v>45.6761</v>
+        <v>31.8718</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.2682</v>
+        <v>8.7195</v>
       </c>
       <c r="G6" t="n">
-        <v>9.8605</v>
+        <v>7.4269</v>
       </c>
       <c r="H6" t="n">
-        <v>12.3066</v>
+        <v>-3.9016</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4461</v>
+        <v>11.3284</v>
       </c>
       <c r="J6" t="n">
-        <v>24.9878</v>
+        <v>37.5634</v>
       </c>
       <c r="K6" t="n">
-        <v>21.1429</v>
+        <v>11.04</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8443</v>
+        <v>26.5227</v>
       </c>
       <c r="M6" t="n">
-        <v>-15.1268</v>
+        <v>-30.1362</v>
       </c>
       <c r="N6" t="n">
-        <v>-8.836500000000001</v>
+        <v>-14.9416</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.2909</v>
+        <v>-15.1945</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.9152</v>
+        <v>16.0951</v>
       </c>
       <c r="Q6" t="n">
-        <v>-22.838</v>
+        <v>-32.1908</v>
       </c>
       <c r="R6" t="n">
-        <v>18.9225</v>
+        <v>48.2859</v>
       </c>
       <c r="S6" t="n">
-        <v>22.5319</v>
+        <v>12.2384</v>
       </c>
       <c r="T6" t="n">
-        <v>18.1735</v>
+        <v>5.2757</v>
       </c>
       <c r="U6" t="n">
-        <v>4.3586</v>
+        <v>6.962400000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>7.9302</v>
+        <v>4.8304</v>
       </c>
       <c r="W6" t="n">
-        <v>25.3532</v>
+        <v>21.224</v>
       </c>
       <c r="X6" t="n">
-        <v>-17.4227</v>
+        <v>-16.3936</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>31.3597</v>
+        <v>38.6288</v>
       </c>
       <c r="E7" t="n">
-        <v>26.8748</v>
+        <v>22.9047</v>
       </c>
       <c r="F7" t="n">
-        <v>4.4846</v>
+        <v>15.724</v>
       </c>
       <c r="G7" t="n">
-        <v>-19.3416</v>
+        <v>4.8289</v>
       </c>
       <c r="H7" t="n">
-        <v>-16.422</v>
+        <v>-16.8207</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.919600000000001</v>
+        <v>21.6494</v>
       </c>
       <c r="J7" t="n">
-        <v>6.5097</v>
+        <v>22.4129</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.173</v>
+        <v>-3.8407</v>
       </c>
       <c r="L7" t="n">
-        <v>8.681800000000001</v>
+        <v>26.2535</v>
       </c>
       <c r="M7" t="n">
-        <v>-25.8512</v>
+        <v>-17.5839</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.2491</v>
+        <v>-12.9797</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.6015</v>
+        <v>-4.604100000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>11.0927</v>
+        <v>3.4799</v>
       </c>
       <c r="Q7" t="n">
-        <v>-28.058</v>
+        <v>-46.3288</v>
       </c>
       <c r="R7" t="n">
-        <v>39.1507</v>
+        <v>49.8088</v>
       </c>
       <c r="S7" t="n">
-        <v>42.5202</v>
+        <v>9.2019</v>
       </c>
       <c r="T7" t="n">
-        <v>27.827</v>
+        <v>3.2339</v>
       </c>
       <c r="U7" t="n">
-        <v>14.6937</v>
+        <v>5.9676</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.9121</v>
+        <v>21.118</v>
       </c>
       <c r="W7" t="n">
-        <v>20.5968</v>
+        <v>43.5867</v>
       </c>
       <c r="X7" t="n">
-        <v>-23.5092</v>
+        <v>-22.4685</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>29.8382</v>
+        <v>34.2609</v>
       </c>
       <c r="E8" t="n">
-        <v>33.9661</v>
+        <v>13.0583</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.1278</v>
+        <v>21.2021</v>
       </c>
       <c r="G8" t="n">
-        <v>44.3466</v>
+        <v>36.1467</v>
       </c>
       <c r="H8" t="n">
-        <v>13.6019</v>
+        <v>2.2043</v>
       </c>
       <c r="I8" t="n">
-        <v>30.7444</v>
+        <v>33.9425</v>
       </c>
       <c r="J8" t="n">
-        <v>74.6345</v>
+        <v>52.0678</v>
       </c>
       <c r="K8" t="n">
-        <v>28.835</v>
+        <v>17.9816</v>
       </c>
       <c r="L8" t="n">
-        <v>45.7995</v>
+        <v>34.0858</v>
       </c>
       <c r="M8" t="n">
-        <v>-30.2881</v>
+        <v>-15.9209</v>
       </c>
       <c r="N8" t="n">
-        <v>-15.2331</v>
+        <v>-15.7775</v>
       </c>
       <c r="O8" t="n">
-        <v>-15.055</v>
+        <v>-0.1434000000000002</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.5282</v>
+        <v>-18.2708</v>
       </c>
       <c r="Q8" t="n">
-        <v>-58.7266</v>
+        <v>-63.0766</v>
       </c>
       <c r="R8" t="n">
-        <v>47.1988</v>
+        <v>44.8058</v>
       </c>
       <c r="S8" t="n">
-        <v>-16.4743</v>
+        <v>9.2424</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.77</v>
+        <v>4.8467</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.704</v>
+        <v>4.3956</v>
       </c>
       <c r="V8" t="n">
-        <v>13.494</v>
+        <v>7.142300000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>30.8287</v>
+        <v>19.2213</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.3345</v>
+        <v>-12.0788</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>24.0961</v>
+        <v>30.0692</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3931</v>
+        <v>11.2295</v>
       </c>
       <c r="F9" t="n">
-        <v>9.703299999999999</v>
+        <v>18.8399</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8289</v>
+        <v>-2.5366</v>
       </c>
       <c r="H9" t="n">
-        <v>-16.8207</v>
+        <v>10.3362</v>
       </c>
       <c r="I9" t="n">
-        <v>21.6494</v>
+        <v>-12.8727</v>
       </c>
       <c r="J9" t="n">
-        <v>22.4129</v>
+        <v>12.5</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.8407</v>
+        <v>16.989</v>
       </c>
       <c r="L9" t="n">
-        <v>26.2535</v>
+        <v>-4.489599999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-17.5839</v>
+        <v>-15.0362</v>
       </c>
       <c r="N9" t="n">
-        <v>-12.9797</v>
+        <v>-6.6528</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.604100000000001</v>
+        <v>-8.383599999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>3.4799</v>
+        <v>-2.1753</v>
       </c>
       <c r="Q9" t="n">
-        <v>-46.3288</v>
+        <v>-48.7213</v>
       </c>
       <c r="R9" t="n">
-        <v>49.8088</v>
+        <v>46.546</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.3312</v>
+        <v>25.2897</v>
       </c>
       <c r="T9" t="n">
-        <v>-5.2778</v>
+        <v>11.5379</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0535999999999997</v>
+        <v>13.7518</v>
       </c>
       <c r="V9" t="n">
-        <v>21.118</v>
+        <v>9.491299999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>43.5867</v>
+        <v>35.9135</v>
       </c>
       <c r="X9" t="n">
-        <v>-22.4685</v>
+        <v>-26.4219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. BARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>20.3915</v>
+        <v>23.9513</v>
       </c>
       <c r="E10" t="n">
-        <v>16.2655</v>
+        <v>34.6015</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1262</v>
+        <v>-10.6503</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4269</v>
+        <v>9.8605</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.9016</v>
+        <v>12.3066</v>
       </c>
       <c r="I10" t="n">
-        <v>11.3284</v>
+        <v>-2.4461</v>
       </c>
       <c r="J10" t="n">
-        <v>37.5634</v>
+        <v>24.9878</v>
       </c>
       <c r="K10" t="n">
-        <v>11.04</v>
+        <v>21.1429</v>
       </c>
       <c r="L10" t="n">
-        <v>26.5227</v>
+        <v>3.8443</v>
       </c>
       <c r="M10" t="n">
-        <v>-30.1362</v>
+        <v>-15.1268</v>
       </c>
       <c r="N10" t="n">
-        <v>-14.9416</v>
+        <v>-8.836500000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-15.1945</v>
+        <v>-6.2909</v>
       </c>
       <c r="P10" t="n">
-        <v>16.0951</v>
+        <v>-3.9152</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32.1908</v>
+        <v>-22.838</v>
       </c>
       <c r="R10" t="n">
-        <v>48.2859</v>
+        <v>18.9225</v>
       </c>
       <c r="S10" t="n">
-        <v>-7.9613</v>
+        <v>10.0754</v>
       </c>
       <c r="T10" t="n">
-        <v>-10.3306</v>
+        <v>7.0988</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3693</v>
+        <v>2.9768</v>
       </c>
       <c r="V10" t="n">
-        <v>4.8304</v>
+        <v>7.9302</v>
       </c>
       <c r="W10" t="n">
-        <v>21.224</v>
+        <v>25.3532</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.3936</v>
+        <v>-17.4227</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>18.5446</v>
+        <v>22.2069</v>
       </c>
       <c r="E11" t="n">
-        <v>13.9143</v>
+        <v>14.5813</v>
       </c>
       <c r="F11" t="n">
-        <v>4.6303</v>
+        <v>7.625599999999999</v>
       </c>
       <c r="G11" t="n">
         <v>1.9252</v>
@@ -1312,13 +1312,13 @@
         <v>23.2728</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8244</v>
+        <v>5.4867</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5693</v>
+        <v>4.236</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.7447</v>
+        <v>1.2503</v>
       </c>
       <c r="V11" t="n">
         <v>3.4846</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>18.3287</v>
+        <v>12.3871</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6356000000000011</v>
+        <v>13.1573</v>
       </c>
       <c r="F12" t="n">
-        <v>17.6936</v>
+        <v>-0.7702999999999993</v>
       </c>
       <c r="G12" t="n">
-        <v>36.1467</v>
+        <v>-19.3416</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2043</v>
+        <v>-16.422</v>
       </c>
       <c r="I12" t="n">
-        <v>33.9425</v>
+        <v>-2.919600000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>52.0678</v>
+        <v>6.5097</v>
       </c>
       <c r="K12" t="n">
-        <v>17.9816</v>
+        <v>-2.173</v>
       </c>
       <c r="L12" t="n">
-        <v>34.0858</v>
+        <v>8.681800000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.9209</v>
+        <v>-25.8512</v>
       </c>
       <c r="N12" t="n">
-        <v>-15.7775</v>
+        <v>-14.2491</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1434000000000002</v>
+        <v>-11.6015</v>
       </c>
       <c r="P12" t="n">
-        <v>-18.2708</v>
+        <v>11.0927</v>
       </c>
       <c r="Q12" t="n">
-        <v>-63.0766</v>
+        <v>-28.058</v>
       </c>
       <c r="R12" t="n">
-        <v>44.8058</v>
+        <v>39.1507</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.6898</v>
+        <v>23.5478</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.5759</v>
+        <v>14.1096</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8864000000000003</v>
+        <v>9.438600000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>7.142300000000001</v>
+        <v>-2.9121</v>
       </c>
       <c r="W12" t="n">
-        <v>19.2213</v>
+        <v>20.5968</v>
       </c>
       <c r="X12" t="n">
-        <v>-12.0788</v>
+        <v>-23.5092</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. MENCIA HERNANDEZ</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8190000000000002</v>
+        <v>2.4291</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2157</v>
+        <v>-0.607</v>
       </c>
       <c r="F13" t="n">
-        <v>7.0348</v>
+        <v>3.0362</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.06619999999999981</v>
+        <v>-2.1385</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6853</v>
+        <v>3.0623</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7515</v>
+        <v>-5.2011</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0866</v>
+        <v>3.1301</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7773</v>
+        <v>4.0736</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8639</v>
+        <v>-0.9433999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0204</v>
+        <v>-5.269</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.09190000000000001</v>
+        <v>-1.0111</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1123</v>
+        <v>-4.2578</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.9576</v>
+        <v>1.74</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.047800000000001</v>
+        <v>-5.002599999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>6.0903</v>
+        <v>6.7426</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4523</v>
+        <v>3.4549</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2029</v>
+        <v>1.2654</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2495</v>
+        <v>2.1894</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3905</v>
+        <v>-0.6269999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7157</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.3252</v>
+        <v>-0.6269999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9431</v>
+        <v>0.6347000000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1378</v>
+        <v>1.6112</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1947</v>
+        <v>-0.9765</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.06619999999999999</v>
+        <v>2.7127</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0182</v>
+        <v>0.7359</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08450000000000001</v>
+        <v>1.9769</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0182</v>
+        <v>3.3609</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0182</v>
+        <v>0.6236999999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.737200000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.6481</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.1122</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.7603</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.87</v>
+        <v>-1.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-3.6976</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2175</v>
+        <v>1.9575</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0068</v>
+        <v>1.552</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.06850000000000001</v>
+        <v>1.9481</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0616</v>
+        <v>-0.3959</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>Y. MENCIA HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.3065</v>
+        <v>0.2497000000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.2278</v>
+        <v>-6.0968</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9212</v>
+        <v>6.3466</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1385</v>
+        <v>-0.06619999999999981</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0623</v>
+        <v>1.6853</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.2011</v>
+        <v>-1.7515</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1301</v>
+        <v>-1.0866</v>
       </c>
       <c r="K15" t="n">
-        <v>4.0736</v>
+        <v>1.7773</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9433999999999999</v>
+        <v>-2.8639</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.269</v>
+        <v>1.0204</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0111</v>
+        <v>-0.09190000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.2578</v>
+        <v>1.1123</v>
       </c>
       <c r="P15" t="n">
-        <v>1.74</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.002599999999999</v>
+        <v>-8.047800000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>6.7426</v>
+        <v>6.0903</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.281</v>
+        <v>1.8831</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3555</v>
+        <v>1.3219</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0745</v>
+        <v>0.5611</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6269999999999999</v>
+        <v>0.3905</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7157</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6269999999999999</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.3319</v>
+        <v>-0.8506</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04710000000000003</v>
+        <v>-1.1378</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.285</v>
+        <v>0.2872</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7127</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7359</v>
+        <v>0.0182</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9769</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3609</v>
+        <v>0.0182</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6236999999999998</v>
+        <v>0.0182</v>
       </c>
       <c r="L16" t="n">
-        <v>2.737200000000001</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6481</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1122</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7603</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.74</v>
+        <v>-0.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6976</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9575</v>
+        <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4147</v>
+        <v>0.0856</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2896</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7043</v>
+        <v>0.1541</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-7.7701</v>
+        <v>-8.7502</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2681</v>
+        <v>3.045500000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.0379</v>
+        <v>-11.7963</v>
       </c>
       <c r="G17" t="n">
         <v>-6.4699</v>
@@ -1780,13 +1780,13 @@
         <v>8.9175</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5814</v>
+        <v>2.6007</v>
       </c>
       <c r="T17" t="n">
-        <v>4.73</v>
+        <v>3.508</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1486</v>
+        <v>-0.907</v>
       </c>
       <c r="V17" t="n">
         <v>-8.1439</v>
@@ -1813,19 +1813,19 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>381.3015</v>
+        <v>413.7225</v>
       </c>
       <c r="E18" t="n">
-        <v>296.8331000000001</v>
+        <v>311.2161</v>
       </c>
       <c r="F18" t="n">
-        <v>84.46950000000001</v>
+        <v>102.5053</v>
       </c>
       <c r="G18" t="n">
         <v>156.0981</v>
       </c>
       <c r="H18" t="n">
-        <v>46.41799999999999</v>
+        <v>46.418</v>
       </c>
       <c r="I18" t="n">
         <v>109.6795</v>
@@ -1849,22 +1849,22 @@
         <v>-89.72490000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>48.9366</v>
+        <v>48.93659999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>-398.0345</v>
       </c>
       <c r="R18" t="n">
-        <v>446.9713999999999</v>
+        <v>446.9714</v>
       </c>
       <c r="S18" t="n">
-        <v>116.8699</v>
+        <v>149.2916</v>
       </c>
       <c r="T18" t="n">
-        <v>64.94329999999999</v>
+        <v>79.3276</v>
       </c>
       <c r="U18" t="n">
-        <v>51.9278</v>
+        <v>69.964</v>
       </c>
       <c r="V18" t="n">
         <v>59.3946</v>
